--- a/artfynd/A 49850-2025 artfynd.xlsx
+++ b/artfynd/A 49850-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,6 +778,200 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129972522</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97668</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ö Römossjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>635142</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6554166</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129972528</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100983</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ö Römossjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>635169</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6554342</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49850-2025 artfynd.xlsx
+++ b/artfynd/A 49850-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129972522</v>
       </c>
       <c r="B3" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129972528</v>
       </c>
       <c r="B4" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49850-2025 artfynd.xlsx
+++ b/artfynd/A 49850-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129972522</v>
       </c>
       <c r="B3" t="n">
-        <v>97671</v>
+        <v>97672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129972528</v>
       </c>
       <c r="B4" t="n">
-        <v>100986</v>
+        <v>100987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49850-2025 artfynd.xlsx
+++ b/artfynd/A 49850-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129972522</v>
       </c>
       <c r="B3" t="n">
-        <v>97672</v>
+        <v>97689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129972528</v>
       </c>
       <c r="B4" t="n">
-        <v>100987</v>
+        <v>101004</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49850-2025 artfynd.xlsx
+++ b/artfynd/A 49850-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129972522</v>
       </c>
       <c r="B3" t="n">
-        <v>97705</v>
+        <v>97707</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129972528</v>
       </c>
       <c r="B4" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49850-2025 artfynd.xlsx
+++ b/artfynd/A 49850-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129972522</v>
       </c>
       <c r="B3" t="n">
-        <v>97707</v>
+        <v>97794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129972528</v>
       </c>
       <c r="B4" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49850-2025 artfynd.xlsx
+++ b/artfynd/A 49850-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126016911</v>
+        <v>129972517</v>
       </c>
       <c r="B2" t="n">
-        <v>97437</v>
+        <v>79946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220250</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Molstaberg, Srm</t>
+          <t>Ö Römossjön, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>635059</v>
+        <v>635174</v>
       </c>
       <c r="R2" t="n">
-        <v>6554209</v>
+        <v>6554274</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Gustaf Eibl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Gustaf Eibl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129972522</v>
+        <v>126016911</v>
       </c>
       <c r="B3" t="n">
-        <v>97794</v>
+        <v>98186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,37 +783,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>220250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ö Römossjön, Srm</t>
+          <t>Molstaberg, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635142</v>
+        <v>635059</v>
       </c>
       <c r="R3" t="n">
-        <v>6554166</v>
+        <v>6554209</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -846,12 +841,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -866,22 +866,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gustaf Eibl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gustaf Eibl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129972528</v>
+        <v>129972522</v>
       </c>
       <c r="B4" t="n">
-        <v>101109</v>
+        <v>97986</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635169</v>
+        <v>635142</v>
       </c>
       <c r="R4" t="n">
-        <v>6554342</v>
+        <v>6554166</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -972,6 +972,103 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129972528</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ö Römossjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>635169</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6554342</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49850-2025 artfynd.xlsx
+++ b/artfynd/A 49850-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129972517</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126016911</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129972522</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,8 +1089,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129972528</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>